--- a/testdata/OpenCart User Data.xlsx
+++ b/testdata/OpenCart User Data.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prash\eclipse-workspace\OnlineShopping\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E50D43E-6C56-4C90-919B-0C61F51CB08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{57667ECA-C762-443C-AD0F-DECF001F7386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Register" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
-  <si>
-    <t>Jagtap</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>userName</t>
   </si>
@@ -40,6 +33,12 @@
   </si>
   <si>
     <t>pqr@gmail.com</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>pqr</t>
   </si>
 </sst>
 </file>
@@ -395,26 +394,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
